--- a/assets/指标测试.xlsx
+++ b/assets/指标测试.xlsx
@@ -112,6 +112,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>最大一家集团客户授信总额</t>
     </r>
     <r>
@@ -183,6 +188,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>非信贷资产减值准备应提数（</t>
     </r>
     <r>
@@ -592,7 +602,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="0"/>
     </font>
     <font>
@@ -1143,7 +1152,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1280,13 +1289,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1294,9 +1297,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1307,9 +1307,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4705,428 +4702,428 @@
       </c>
     </row>
     <row r="96" ht="38" customHeight="1" spans="1:10">
-      <c r="A96" s="45">
+      <c r="A96" s="13">
         <v>30</v>
       </c>
-      <c r="B96" s="46" t="s">
+      <c r="B96" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="C96" s="47">
+      <c r="C96" s="15">
         <v>840949.64</v>
       </c>
-      <c r="D96" s="47">
+      <c r="D96" s="15">
         <v>840540.76</v>
       </c>
-      <c r="E96" s="47">
+      <c r="E96" s="15">
         <v>846049.69</v>
       </c>
-      <c r="F96" s="48">
+      <c r="F96" s="46">
         <v>794308.72</v>
       </c>
-      <c r="G96" s="49">
+      <c r="G96" s="47">
         <v>1010197.68</v>
       </c>
-      <c r="H96" s="48">
+      <c r="H96" s="46">
         <v>1101036.48</v>
       </c>
-      <c r="I96" s="48">
+      <c r="I96" s="46">
         <v>1229676.79</v>
       </c>
-      <c r="J96" s="48">
+      <c r="J96" s="46">
         <v>1091722.29</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="1:10">
-      <c r="A97" s="45"/>
-      <c r="B97" s="50" t="s">
+      <c r="A97" s="13"/>
+      <c r="B97" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="C97" s="47">
+      <c r="C97" s="15">
         <v>11362223.79</v>
       </c>
-      <c r="D97" s="47">
+      <c r="D97" s="15">
         <v>11847437.55</v>
       </c>
-      <c r="E97" s="47">
+      <c r="E97" s="15">
         <v>11887047.27</v>
       </c>
-      <c r="F97" s="48">
+      <c r="F97" s="46">
         <v>12508280.65</v>
       </c>
-      <c r="G97" s="49">
+      <c r="G97" s="47">
         <v>13050675.84</v>
       </c>
-      <c r="H97" s="48">
+      <c r="H97" s="46">
         <v>13076871.14</v>
       </c>
-      <c r="I97" s="48">
+      <c r="I97" s="46">
         <v>13968380.21</v>
       </c>
-      <c r="J97" s="48">
+      <c r="J97" s="46">
         <v>14162978.31</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="1:10">
-      <c r="A98" s="51"/>
-      <c r="B98" s="52" t="s">
+      <c r="A98" s="48"/>
+      <c r="B98" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="C98" s="53">
+      <c r="C98" s="50">
         <f t="shared" ref="C98:J98" si="40">C96/C97*100</f>
         <v>7.40127685867381</v>
       </c>
-      <c r="D98" s="53">
+      <c r="D98" s="50">
         <f t="shared" si="40"/>
         <v>7.09470513309437</v>
       </c>
-      <c r="E98" s="53">
+      <c r="E98" s="50">
         <f t="shared" si="40"/>
         <v>7.11740830824508</v>
       </c>
-      <c r="F98" s="53">
+      <c r="F98" s="50">
         <f t="shared" si="40"/>
         <v>6.35026301556481</v>
       </c>
-      <c r="G98" s="54">
+      <c r="G98" s="51">
         <f t="shared" si="40"/>
         <v>7.74057751786133</v>
       </c>
-      <c r="H98" s="53">
+      <c r="H98" s="50">
         <f t="shared" si="40"/>
         <v>8.4197241695845</v>
       </c>
-      <c r="I98" s="53">
+      <c r="I98" s="50">
         <f t="shared" si="40"/>
         <v>8.80328836638962</v>
       </c>
-      <c r="J98" s="53">
+      <c r="J98" s="50">
         <f t="shared" si="40"/>
         <v>7.70828187478881</v>
       </c>
     </row>
     <row r="99" ht="30" customHeight="1" spans="1:10">
-      <c r="A99" s="45">
+      <c r="A99" s="13">
         <v>31</v>
       </c>
-      <c r="B99" s="46" t="s">
+      <c r="B99" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="C99" s="47">
+      <c r="C99" s="15">
         <f t="shared" ref="C99:J99" si="41">C48</f>
         <v>22328.49</v>
       </c>
-      <c r="D99" s="47">
+      <c r="D99" s="15">
         <f t="shared" si="41"/>
         <v>50194.76</v>
       </c>
-      <c r="E99" s="47">
+      <c r="E99" s="15">
         <f t="shared" si="41"/>
         <v>85400.07</v>
       </c>
-      <c r="F99" s="47">
+      <c r="F99" s="15">
         <f t="shared" si="41"/>
         <v>101598.4</v>
       </c>
-      <c r="G99" s="55">
+      <c r="G99" s="16">
         <f t="shared" si="41"/>
         <v>26212.41</v>
       </c>
-      <c r="H99" s="47">
+      <c r="H99" s="15">
         <f t="shared" si="41"/>
         <v>61757.73</v>
       </c>
-      <c r="I99" s="47">
+      <c r="I99" s="15">
         <f t="shared" si="41"/>
         <v>92608.69</v>
       </c>
-      <c r="J99" s="47">
+      <c r="J99" s="15">
         <f t="shared" si="41"/>
         <v>112042.05</v>
       </c>
     </row>
     <row r="100" ht="27" customHeight="1" spans="1:10">
-      <c r="A100" s="45"/>
-      <c r="B100" s="50" t="s">
+      <c r="A100" s="13"/>
+      <c r="B100" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="C100" s="47" t="e">
+      <c r="C100" s="15" t="e">
         <f>(#REF!+C88)/2</f>
         <v>#REF!</v>
       </c>
-      <c r="D100" s="47" t="e">
+      <c r="D100" s="15" t="e">
         <f>(D88+#REF!)/2</f>
         <v>#REF!</v>
       </c>
-      <c r="E100" s="47" t="e">
+      <c r="E100" s="15" t="e">
         <f>(E88+#REF!)/2</f>
         <v>#REF!</v>
       </c>
-      <c r="F100" s="48" t="e">
+      <c r="F100" s="46" t="e">
         <f>(F88+#REF!)/2</f>
         <v>#REF!</v>
       </c>
-      <c r="G100" s="56">
+      <c r="G100" s="52">
         <f>(G88+F88)/2</f>
         <v>9432885.355</v>
       </c>
-      <c r="H100" s="57">
+      <c r="H100" s="53">
         <f>(H88+F88)/2</f>
         <v>9525712.92</v>
       </c>
-      <c r="I100" s="57">
+      <c r="I100" s="53">
         <f>(I88+F88)/2</f>
         <v>9655997.565</v>
       </c>
-      <c r="J100" s="57">
+      <c r="J100" s="53">
         <f>(J88+F88)/2</f>
         <v>9583435.895</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:10">
-      <c r="A101" s="51"/>
-      <c r="B101" s="52" t="s">
+      <c r="A101" s="48"/>
+      <c r="B101" s="49" t="s">
         <v>93</v>
       </c>
-      <c r="C101" s="53" t="e">
+      <c r="C101" s="50" t="e">
         <f>C99/C100*100*4</f>
         <v>#REF!</v>
       </c>
-      <c r="D101" s="53" t="e">
+      <c r="D101" s="50" t="e">
         <f>D99/D100*100*2</f>
         <v>#REF!</v>
       </c>
-      <c r="E101" s="53" t="e">
+      <c r="E101" s="50" t="e">
         <f>E99/E100*100*4/3</f>
         <v>#REF!</v>
       </c>
-      <c r="F101" s="53" t="e">
+      <c r="F101" s="50" t="e">
         <f>F99/F100*100</f>
         <v>#REF!</v>
       </c>
-      <c r="G101" s="54">
+      <c r="G101" s="51">
         <f>G99/G100*100*4</f>
         <v>1.11153306813406</v>
       </c>
-      <c r="H101" s="53">
+      <c r="H101" s="50">
         <f>H99/H100*100*2</f>
         <v>1.29665318530301</v>
       </c>
-      <c r="I101" s="53">
+      <c r="I101" s="50">
         <f>I99/I100*100*4/3</f>
         <v>1.27877262294373</v>
       </c>
-      <c r="J101" s="53">
+      <c r="J101" s="50">
         <f>J99/J100*100</f>
         <v>1.16912192273813</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="1:10">
-      <c r="A102" s="45">
+      <c r="A102" s="13">
         <v>32</v>
       </c>
-      <c r="B102" s="46" t="s">
+      <c r="B102" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="C102" s="47">
+      <c r="C102" s="15">
         <v>18538.64</v>
       </c>
-      <c r="D102" s="47">
+      <c r="D102" s="15">
         <v>38481.93</v>
       </c>
-      <c r="E102" s="47">
+      <c r="E102" s="15">
         <v>44285.8</v>
       </c>
-      <c r="F102" s="47">
+      <c r="F102" s="15">
         <v>54479</v>
       </c>
-      <c r="G102" s="55">
+      <c r="G102" s="16">
         <v>15946.06</v>
       </c>
-      <c r="H102" s="47">
+      <c r="H102" s="15">
         <v>32964.91</v>
       </c>
-      <c r="I102" s="47">
+      <c r="I102" s="15">
         <v>32964.91</v>
       </c>
-      <c r="J102" s="47">
+      <c r="J102" s="15">
         <v>49194.81</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="1:10">
-      <c r="A103" s="45"/>
-      <c r="B103" s="50" t="s">
+      <c r="A103" s="13"/>
+      <c r="B103" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="C103" s="47" t="e">
+      <c r="C103" s="15" t="e">
         <f>(#REF!+C88)/2</f>
         <v>#REF!</v>
       </c>
-      <c r="D103" s="47" t="e">
+      <c r="D103" s="15" t="e">
         <f>(#REF!+D88)/2</f>
         <v>#REF!</v>
       </c>
-      <c r="E103" s="47" t="e">
+      <c r="E103" s="15" t="e">
         <f>(#REF!+E88)/2</f>
         <v>#REF!</v>
       </c>
-      <c r="F103" s="47" t="e">
+      <c r="F103" s="15" t="e">
         <f>(#REF!+F88)/2</f>
         <v>#REF!</v>
       </c>
-      <c r="G103" s="49">
+      <c r="G103" s="47">
         <f t="shared" ref="G103:J103" si="42">G100</f>
         <v>9432885.355</v>
       </c>
-      <c r="H103" s="48">
+      <c r="H103" s="46">
         <f t="shared" si="42"/>
         <v>9525712.92</v>
       </c>
-      <c r="I103" s="48">
+      <c r="I103" s="46">
         <f t="shared" si="42"/>
         <v>9655997.565</v>
       </c>
-      <c r="J103" s="48">
+      <c r="J103" s="46">
         <f t="shared" si="42"/>
         <v>9583435.895</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="1:10">
-      <c r="A104" s="51"/>
-      <c r="B104" s="52" t="s">
+      <c r="A104" s="48"/>
+      <c r="B104" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="C104" s="53" t="e">
+      <c r="C104" s="50" t="e">
         <f>C102/C103*100*4</f>
         <v>#REF!</v>
       </c>
-      <c r="D104" s="53" t="e">
+      <c r="D104" s="50" t="e">
         <f>D102/D103*100*2</f>
         <v>#REF!</v>
       </c>
-      <c r="E104" s="53" t="e">
+      <c r="E104" s="50" t="e">
         <f>E102/E103*100*4/3</f>
         <v>#REF!</v>
       </c>
-      <c r="F104" s="53" t="e">
+      <c r="F104" s="50" t="e">
         <f>F102/F103*100</f>
         <v>#REF!</v>
       </c>
-      <c r="G104" s="54">
+      <c r="G104" s="51">
         <f>G102/G103*100*4</f>
         <v>0.676190132706219</v>
       </c>
-      <c r="H104" s="53">
+      <c r="H104" s="50">
         <f>H102/H103*100*2</f>
         <v>0.692124784293835</v>
       </c>
-      <c r="I104" s="53">
+      <c r="I104" s="50">
         <f>I102/I103*100*4/3</f>
         <v>0.455190807966337</v>
       </c>
-      <c r="J104" s="53">
+      <c r="J104" s="50">
         <f>J102/J103*100</f>
         <v>0.513331654106087</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="1:10">
-      <c r="A105" s="45">
+      <c r="A105" s="13">
         <v>32</v>
       </c>
-      <c r="B105" s="46" t="s">
+      <c r="B105" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="C105" s="47">
+      <c r="C105" s="15">
         <v>18538.64</v>
       </c>
-      <c r="D105" s="47">
+      <c r="D105" s="15">
         <v>38481.93</v>
       </c>
-      <c r="E105" s="47">
+      <c r="E105" s="15">
         <v>44285.8</v>
       </c>
-      <c r="F105" s="47">
+      <c r="F105" s="15">
         <v>219702.48</v>
       </c>
-      <c r="G105" s="55">
+      <c r="G105" s="16">
         <v>61724.37</v>
       </c>
-      <c r="H105" s="47">
+      <c r="H105" s="15">
         <v>125131.24</v>
       </c>
-      <c r="I105" s="47">
+      <c r="I105" s="15">
         <v>188444.56</v>
       </c>
-      <c r="J105" s="47">
+      <c r="J105" s="15">
         <v>254314.57</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="1:10">
-      <c r="A106" s="45"/>
-      <c r="B106" s="50" t="s">
+      <c r="A106" s="13"/>
+      <c r="B106" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="C106" s="47" t="e">
+      <c r="C106" s="15" t="e">
         <f>(#REF!+C91)/2</f>
         <v>#REF!</v>
       </c>
-      <c r="D106" s="47" t="e">
+      <c r="D106" s="15" t="e">
         <f>(#REF!+D91)/2</f>
         <v>#REF!</v>
       </c>
-      <c r="E106" s="47" t="e">
+      <c r="E106" s="15" t="e">
         <f>(#REF!+E91)/2</f>
         <v>#REF!</v>
       </c>
-      <c r="F106" s="47">
+      <c r="F106" s="15">
         <v>12587223.05</v>
       </c>
-      <c r="G106" s="49">
+      <c r="G106" s="47">
         <v>13708585.56</v>
       </c>
-      <c r="H106" s="48">
+      <c r="H106" s="46">
         <v>13583556.43</v>
       </c>
-      <c r="I106" s="48">
+      <c r="I106" s="46">
         <v>14031354.81</v>
       </c>
-      <c r="J106" s="48">
+      <c r="J106" s="46">
         <v>14164402.93</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="1:10">
-      <c r="A107" s="51"/>
-      <c r="B107" s="52" t="s">
+      <c r="A107" s="48"/>
+      <c r="B107" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="C107" s="53" t="e">
+      <c r="C107" s="50" t="e">
         <f>C105/C106*100*4</f>
         <v>#REF!</v>
       </c>
-      <c r="D107" s="53" t="e">
+      <c r="D107" s="50" t="e">
         <f>D105/D106*100*2</f>
         <v>#REF!</v>
       </c>
-      <c r="E107" s="53" t="e">
+      <c r="E107" s="50" t="e">
         <f>E105/E106*100*4/3</f>
         <v>#REF!</v>
       </c>
-      <c r="F107" s="53">
+      <c r="F107" s="50">
         <f>F105/F106*100</f>
         <v>1.74544042897532</v>
       </c>
-      <c r="G107" s="54">
+      <c r="G107" s="51">
         <f>G105/G106*100*4</f>
         <v>1.80104270363543</v>
       </c>
-      <c r="H107" s="53">
+      <c r="H107" s="50">
         <f>H105/H106*100*2</f>
         <v>1.84239290564054</v>
       </c>
-      <c r="I107" s="53">
+      <c r="I107" s="50">
         <f>I105/I106*100*4/3</f>
         <v>1.79069959198996</v>
       </c>
-      <c r="J107" s="53">
+      <c r="J107" s="50">
         <f>J105/J106*100</f>
         <v>1.79544857101859</v>
       </c>
